--- a/data/trans_orig/IP07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general percibida por adulto en 2007 (tasa de respuesta: 99,81%)</t>
+          <t>Menores según su salud general percibida por el adulto en 2007 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22360</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17900</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32106</t>
+          <t>31703</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30820</t>
+          <t>30770</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49815</t>
+          <t>49328</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45031</t>
+          <t>45793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>62950</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47965</t>
+          <t>46976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64612</t>
+          <t>64750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97304</t>
+          <t>97407</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122701</t>
+          <t>122057</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28036</t>
+          <t>27639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44343</t>
+          <t>43332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30368</t>
+          <t>30678</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46548</t>
+          <t>46602</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63120</t>
+          <t>63930</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86610</t>
+          <t>86146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -1450,47 +1450,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6566</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2647</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>671</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2647</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48085</t>
+          <t>46718</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68853</t>
+          <t>68737</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41524</t>
+          <t>40948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61905</t>
+          <t>61404</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>94303</t>
+          <t>92922</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>122884</t>
+          <t>122703</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111608</t>
+          <t>111646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136450</t>
+          <t>137548</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106178</t>
+          <t>105337</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132175</t>
+          <t>130991</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>225367</t>
+          <t>223662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260195</t>
+          <t>258818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58959</t>
+          <t>59394</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81534</t>
+          <t>82807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63306</t>
+          <t>62205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>86006</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128666</t>
+          <t>129210</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158563</t>
+          <t>161241</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15983</t>
+          <t>16232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20230</t>
+          <t>20153</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35156</t>
+          <t>34845</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21760</t>
+          <t>21563</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>36654</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45913</t>
+          <t>45930</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>67569</t>
+          <t>66536</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44437</t>
+          <t>43980</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62629</t>
+          <t>62275</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58558</t>
+          <t>59046</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77736</t>
+          <t>78182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>108702</t>
+          <t>109331</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133684</t>
+          <t>135159</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>50,23%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35304</t>
+          <t>35403</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52733</t>
+          <t>52462</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28644</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>45807</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68663</t>
+          <t>69305</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92886</t>
+          <t>93100</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16052</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31702</t>
+          <t>32340</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49646</t>
+          <t>49735</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30290</t>
+          <t>29881</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>47391</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>67537</t>
+          <t>67813</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>92050</t>
+          <t>93044</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82783</t>
+          <t>83166</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106445</t>
+          <t>105015</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>89680</t>
+          <t>89263</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>113105</t>
+          <t>111855</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>177473</t>
+          <t>178117</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>210082</t>
+          <t>210705</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,83%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43847</t>
+          <t>43751</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64434</t>
+          <t>63480</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48452</t>
+          <t>49008</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69581</t>
+          <t>69791</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>98993</t>
+          <t>98819</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>129713</t>
+          <t>129232</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29609</t>
+          <t>29637</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>23169</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41204</t>
+          <t>40724</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>124187</t>
+          <t>124240</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>157613</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>126943</t>
+          <t>125719</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>160553</t>
+          <t>160224</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>259826</t>
+          <t>259266</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>309685</t>
+          <t>307498</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>303473</t>
+          <t>307527</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>344318</t>
+          <t>347175</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>323699</t>
+          <t>322165</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>363392</t>
+          <t>364878</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>638179</t>
+          <t>637028</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>701740</t>
+          <t>698474</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>184527</t>
+          <t>185137</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>221686</t>
+          <t>223318</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>188960</t>
+          <t>189871</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>227575</t>
+          <t>229456</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>383793</t>
+          <t>386189</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>439661</t>
+          <t>440997</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general percibida por adulto en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Menores según su salud general percibida por el adulto en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14565</t>
+          <t>14881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22849</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38305</t>
+          <t>38843</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25562</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42536</t>
+          <t>43723</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53793</t>
+          <t>53149</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76243</t>
+          <t>76607</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59927</t>
+          <t>60197</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79974</t>
+          <t>80345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59220</t>
+          <t>59643</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79230</t>
+          <t>80223</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>126006</t>
+          <t>126818</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152766</t>
+          <t>153062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33368</t>
+          <t>33020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51340</t>
+          <t>51917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>28615</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45361</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67390</t>
+          <t>67491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92603</t>
+          <t>90880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36628</t>
+          <t>36671</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56576</t>
+          <t>56259</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50154</t>
+          <t>50142</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73094</t>
+          <t>73450</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>92561</t>
+          <t>93484</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>122690</t>
+          <t>123914</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111422</t>
+          <t>110246</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135677</t>
+          <t>135996</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117058</t>
+          <t>117588</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144722</t>
+          <t>145286</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>234901</t>
+          <t>234704</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273264</t>
+          <t>272340</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49769</t>
+          <t>49452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71254</t>
+          <t>71060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61124</t>
+          <t>59424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84888</t>
+          <t>84416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115546</t>
+          <t>116455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147776</t>
+          <t>148995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31593</t>
+          <t>32049</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50274</t>
+          <t>51100</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28789</t>
+          <t>27805</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46277</t>
+          <t>45381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64204</t>
+          <t>65464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>90487</t>
+          <t>90573</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65267</t>
+          <t>64842</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86900</t>
+          <t>86225</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74738</t>
+          <t>75696</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96115</t>
+          <t>96409</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>146644</t>
+          <t>146795</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176808</t>
+          <t>175905</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>28692</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45581</t>
+          <t>45971</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24288</t>
+          <t>24450</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40928</t>
+          <t>39708</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56265</t>
+          <t>57282</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79483</t>
+          <t>80447</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33176</t>
+          <t>33561</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51684</t>
+          <t>52495</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31173</t>
+          <t>30448</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48777</t>
+          <t>48473</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>69540</t>
+          <t>68912</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>94056</t>
+          <t>93838</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71749</t>
+          <t>72775</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93760</t>
+          <t>94068</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73889</t>
+          <t>72660</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94731</t>
+          <t>94810</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152859</t>
+          <t>152587</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181907</t>
+          <t>184256</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,56%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33394</t>
+          <t>32417</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52204</t>
+          <t>50670</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40769</t>
+          <t>40972</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60970</t>
+          <t>59790</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>78433</t>
+          <t>79144</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>103828</t>
+          <t>104862</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,91%</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9884</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22463</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41115</t>
+          <t>41103</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>142190</t>
+          <t>141628</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>177439</t>
+          <t>177477</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>152068</t>
+          <t>151536</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>190399</t>
+          <t>190205</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>305014</t>
+          <t>303781</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>356232</t>
+          <t>354970</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>332218</t>
+          <t>332494</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>375280</t>
+          <t>376184</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>348496</t>
+          <t>347373</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>393479</t>
+          <t>394203</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>692281</t>
+          <t>692393</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>756128</t>
+          <t>753110</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,62%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>161351</t>
+          <t>160800</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>199092</t>
+          <t>199070</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>170573</t>
+          <t>170322</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>210301</t>
+          <t>209592</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>341915</t>
+          <t>345202</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>397047</t>
+          <t>398560</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general percibida por adulto en 2016 (tasa de respuesta: 99,48%)</t>
+          <t>Menores según su salud general percibida por el adulto en 2016 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>531</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19696</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>16887</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32259</t>
+          <t>32756</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30652</t>
+          <t>30921</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47251</t>
+          <t>46883</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30095</t>
+          <t>29564</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45585</t>
+          <t>46730</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>63663</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87817</t>
+          <t>87349</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68108</t>
+          <t>67914</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85665</t>
+          <t>85647</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62284</t>
+          <t>61332</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79924</t>
+          <t>79475</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>134361</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>159573</t>
+          <t>161575</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>63,53%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>15320</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29415</t>
+          <t>28908</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22018</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>38291</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>41129</t>
+          <t>41796</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64418</t>
+          <t>63837</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65235</t>
+          <t>65550</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87101</t>
+          <t>86795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88723</t>
+          <t>87937</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114458</t>
+          <t>113640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161170</t>
+          <t>158904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194448</t>
+          <t>192469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94814</t>
+          <t>95079</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117091</t>
+          <t>116929</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110889</t>
+          <t>111357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136668</t>
+          <t>137291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,47 +9201,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>53,33%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>230627</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>213010</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>247137</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>49,54%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>45,76%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>53,09%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>230627</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>212090</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>246201</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>49,54%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>45,56%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>52,89%</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12058</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>25908</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21992</t>
+          <t>22329</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36483</t>
+          <t>37062</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58780</t>
+          <t>58321</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66544</t>
+          <t>66997</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88391</t>
+          <t>89662</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53635</t>
+          <t>52623</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75883</t>
+          <t>75677</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>125833</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>157898</t>
+          <t>158289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78738</t>
+          <t>78536</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101936</t>
+          <t>101443</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79519</t>
+          <t>79622</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101927</t>
+          <t>101976</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>164883</t>
+          <t>161570</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>196996</t>
+          <t>197134</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8319</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12368</t>
+          <t>11720</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16616</t>
+          <t>16194</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32158</t>
+          <t>31282</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27671</t>
+          <t>27425</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33412</t>
+          <t>32653</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54721</t>
+          <t>53625</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61672</t>
+          <t>62172</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84170</t>
+          <t>83885</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61715</t>
+          <t>60678</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83735</t>
+          <t>82872</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>127643</t>
+          <t>128943</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>159452</t>
+          <t>158797</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62510</t>
+          <t>63505</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>84364</t>
+          <t>85568</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>66474</t>
+          <t>66237</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>87432</t>
+          <t>87413</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>135844</t>
+          <t>137077</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>167077</t>
+          <t>167358</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,48%</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>791</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18955</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>21270</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>35510</t>
+          <t>35043</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63457</t>
+          <t>63945</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>89609</t>
+          <t>90433</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>74469</t>
+          <t>74828</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>103999</t>
+          <t>104898</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>145624</t>
+          <t>146596</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>183776</t>
+          <t>185168</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>243966</t>
+          <t>243401</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>284085</t>
+          <t>283171</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>252359</t>
+          <t>253269</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>293813</t>
+          <t>295461</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>508615</t>
+          <t>507798</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>570362</t>
+          <t>566974</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>324372</t>
+          <t>327234</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>367000</t>
+          <t>367850</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>342881</t>
+          <t>339023</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>385964</t>
+          <t>383060</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>678899</t>
+          <t>678694</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>741576</t>
+          <t>741288</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general percibida por adulto en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según su salud general percibida por el adulto en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4929</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13697</t>
+          <t>14043</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21542</t>
+          <t>21617</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>20810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31569</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18445</t>
+          <t>19559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30284</t>
+          <t>30285</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42836</t>
+          <t>42838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58829</t>
+          <t>59038</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,63%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15034</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26161</t>
+          <t>25498</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21006</t>
+          <t>20702</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32727</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39405</t>
+          <t>39590</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>55067</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,29%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25898</t>
+          <t>25845</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42169</t>
+          <t>41604</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28685</t>
+          <t>28924</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47555</t>
+          <t>47304</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>59219</t>
+          <t>59649</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>84144</t>
+          <t>85758</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58766</t>
+          <t>60430</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80489</t>
+          <t>80917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68934</t>
+          <t>69479</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91894</t>
+          <t>92215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134418</t>
+          <t>134994</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166108</t>
+          <t>165055</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43522</t>
+          <t>43157</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64085</t>
+          <t>63213</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50589</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71648</t>
+          <t>73861</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99694</t>
+          <t>100172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129169</t>
+          <t>127994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>11770</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>17925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30928</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49959</t>
+          <t>48507</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37749</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63158</t>
+          <t>63450</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>73489</t>
+          <t>74111</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>106032</t>
+          <t>104740</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58251</t>
+          <t>56352</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81428</t>
+          <t>79444</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74146</t>
+          <t>73813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102144</t>
+          <t>102621</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139218</t>
+          <t>138672</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>175643</t>
+          <t>174191</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48093</t>
+          <t>49073</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71698</t>
+          <t>72952</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55853</t>
+          <t>55983</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83674</t>
+          <t>82592</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112844</t>
+          <t>111714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148601</t>
+          <t>148528</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29974</t>
+          <t>34087</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>39137</t>
+          <t>37989</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33178</t>
+          <t>34194</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59263</t>
+          <t>61142</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55632</t>
+          <t>55177</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103942</t>
+          <t>100339</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>97121</t>
+          <t>94766</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>148990</t>
+          <t>147831</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77032</t>
+          <t>72505</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126749</t>
+          <t>125436</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120542</t>
+          <t>122828</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>162997</t>
+          <t>165233</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>207208</t>
+          <t>216015</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>280003</t>
+          <t>280739</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,32%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>86448</t>
+          <t>88192</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>156459</t>
+          <t>162477</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67919</t>
+          <t>69414</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105090</t>
+          <t>103795</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>165843</t>
+          <t>163365</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>252827</t>
+          <t>254082</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42397</t>
+          <t>43706</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28009</t>
+          <t>27555</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>27346</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62267</t>
+          <t>61701</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>110284</t>
+          <t>109651</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>146851</t>
+          <t>146244</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>142360</t>
+          <t>141959</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>200330</t>
+          <t>195018</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>262206</t>
+          <t>265765</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>328439</t>
+          <t>330636</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>238111</t>
+          <t>234971</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>298724</t>
+          <t>296518</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>309217</t>
+          <t>308951</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>367424</t>
+          <t>365508</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>561897</t>
+          <t>565373</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>644838</t>
+          <t>648112</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,38%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>216159</t>
+          <t>214810</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>300801</t>
+          <t>299724</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>216796</t>
+          <t>216137</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>270262</t>
+          <t>268832</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>446023</t>
+          <t>447564</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>545985</t>
+          <t>545543</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
